--- a/pages/hathitrustLinks.xlsx
+++ b/pages/hathitrustLinks.xlsx
@@ -5,16 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leblance/Documents/Spurgeon/3-DataExtraction/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leblance/Documents/Spurgeon/3-DataExtraction/pages/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6100FC6-47CC-3549-BDAB-F27518F9326B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA2AC92-3512-904C-9019-AD69F3CB9EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="680" windowWidth="28080" windowHeight="18440" activeTab="1" xr2:uid="{BF3ACDA5-550D-8943-9A5A-8ED6A7642740}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{BF3ACDA5-550D-8943-9A5A-8ED6A7642740}"/>
   </bookViews>
   <sheets>
-    <sheet name="Part 2" sheetId="1" r:id="rId1"/>
-    <sheet name="Part3" sheetId="2" r:id="rId2"/>
+    <sheet name="Part1" sheetId="6" r:id="rId1"/>
+    <sheet name="Part2" sheetId="1" r:id="rId2"/>
+    <sheet name="Part3" sheetId="2" r:id="rId3"/>
+    <sheet name="AppA" sheetId="3" r:id="rId4"/>
+    <sheet name="AppB" sheetId="4" r:id="rId5"/>
+    <sheet name="AppC" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="1189">
   <si>
     <t>Page number</t>
   </si>
@@ -1366,13 +1370,2254 @@
   </si>
   <si>
     <t>https://hdl.handle.net/2027/mdp.39015066185086?urlappend=%3Bseq=482</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=17</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=18</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=19</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=20</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=21</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=22</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=23</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=24</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=25</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=26</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=27</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=28</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=29</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=30</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=31</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=32</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=33</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=34</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=35</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=36</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=37</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=38</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=39</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=40</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=41</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=42</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=43</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=44</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=45</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=46</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=47</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=48</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=49</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=50</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=51</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=52</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=53</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=54</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=55</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=56</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=57</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=58</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=59</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=60</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=61</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=62</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=67</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=68</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=69</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=70</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=75</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=76</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=77</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=78</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=79</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=80</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=81</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=82</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=83</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=84</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=85</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=86</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=87</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=88</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=89</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=90</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=91</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=92</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=93</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=94</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=95</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=96</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=97</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=98</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=99</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=100</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=101</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=102</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=103</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=104</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=105</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=106</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=107</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=108</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=109</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=110</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=111</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=112</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=113</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=114</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=115</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=116</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=117</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=118</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=119</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=120</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=121</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=122</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=123</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=124</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=125</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=126</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=127</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=128</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=129</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=130</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=131</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=148</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=155</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=156</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=157</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=158</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=159</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=160</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=161</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=162</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=163</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=164</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=165</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=166</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=167</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=168</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=169</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=170</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=171</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=172</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=173</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=174</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=175</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=176</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=177</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=178</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=179</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=180</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=181</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=182</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=183</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=184</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=185</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=186</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=187</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=188</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=189</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=190</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=191</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=192</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=193</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=194</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=195</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=196</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=197</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=198</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=199</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=200</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=201</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=202</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=203</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=204</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=205</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=206</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=207</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=208</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=209</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=210</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=211</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=212</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=213</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=214</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=215</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=216</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=217</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=218</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=219</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=220</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=221</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=222</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=223</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=224</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=225</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=226</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=227</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=228</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=229</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=230</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=231</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=232</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=233</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=234</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=235</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=236</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=237</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=238</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=239</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=240</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=241</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=242</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=243</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=244</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=245</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=246</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=247</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=248</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=249</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=250</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=251</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=252</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=253</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=254</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=255</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=256</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=257</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=258</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=259</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=260</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=261</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=262</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=263</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=266</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=267</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=268</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=269</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=270</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=271</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=272</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=273</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=274</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=275</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=276</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=277</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=278</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=279</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=280</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=281</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=282</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=283</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=284</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=285</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=286</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=287</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=288</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=289</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=290</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=291</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=155</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=156</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=157</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=158</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=159</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=160</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=161</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=162</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=167</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=168</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=169</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=170</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=171</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=172</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=173</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=174</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=175</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=176</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=177</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=178</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=179</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=180</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=181</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=182</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=183</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=184</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=189</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=190</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=191</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=192</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=193</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=194</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=199</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=200</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=201</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=202</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=203</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=204</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=205</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=206</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=207</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=208</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=209</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=210</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=211</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=212</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=213</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=214</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=215</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=216</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=217</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=218</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=219</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=220</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=221</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=222</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=223</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=224</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=225</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=226</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=231</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=232</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=237</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=238</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=243</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=244</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=245</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=246</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=247</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=248</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=249</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=250</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=251</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=252</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=257</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=258</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=259</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=260</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=261</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=262</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=263</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=264</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=269</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=270</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=271</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=272</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=273</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=274</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=275</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=276</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=277</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=278</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=279</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=283</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=284</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=285</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=286</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=287</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=288</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=289</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=290</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=291</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=292</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=293</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=294</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=295</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=296</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=297</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=298</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=299</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=300</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=301</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=302</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=303</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=304</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=305</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=306</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=307</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=308</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=309</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=310</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=311</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=312</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=313</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=314</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=315</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=316</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=317</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=318</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=319</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=320</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=321</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=322</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=323</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=324</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=325</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=326</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=327</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=328</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=329</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=330</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=331</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=332</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=333</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=334</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=339</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=340</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=341</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=342</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=343</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=344</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=345</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=346</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=347</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=348</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=349</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=350</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=351</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=352</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=353</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=354</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=355</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=356</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=357</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=358</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=359</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=360</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=361</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=362</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=363</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=364</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=365</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=366</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=367</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=368</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=369</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=370</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=371</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=372</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=373</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=374</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=375</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=376</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=377</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=378</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=379</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=380</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=381</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=382</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=383</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=384</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=385</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=386</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=387</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=388</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=389</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=390</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=391</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=392</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=393</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=394</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=395</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=396</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=397</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=398</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=399</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=400</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=401</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=402</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=403</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=404</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=405</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=406</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=407</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=408</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=409</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=410</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=411</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=412</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=413</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=414</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=415</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=416</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=417</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=418</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=419</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=420</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=421</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=422</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=423</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=424</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=425</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=426</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=427</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=428</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=429</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=430</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=431</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=432</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=433</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=434</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=435</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=436</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=437</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=438</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=439</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=440</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=441</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=442</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=443</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=444</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=445</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=446</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=447</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=448</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=449</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=450</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=451</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=452</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=453</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=454</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=455</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=456</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=457</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=458</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=459</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=460</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=461</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=462</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=463</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=464</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=465</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=466</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=467</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=468</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=469</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=470</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=471</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=472</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=473</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=474</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=475</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=476</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=477</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=478</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=479</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=480</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=481</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=482</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=483</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=484</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=485</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=486</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=487</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=488</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=489</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=490</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=491</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=492</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=493</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=494</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=495</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=496</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=497</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=498</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=499</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=500</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=501</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=502</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=503</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=504</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=505</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=506</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=507</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=508</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=509</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=510</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=511</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=512</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=513</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=514</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=515</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=516</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=517</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=518</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=519</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=520</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=521</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=522</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=523</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=524</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=525</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=526</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=527</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=528</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=529</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=530</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=531</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=532</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=533</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=534</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=535</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=536</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=537</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=538</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=539</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=540</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=541</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=542</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=543</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=544</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=545</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=546</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=547</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=548</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=549</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=550</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=551</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=552</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=553</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=554</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=555</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=556</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=557</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=558</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=559</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=560</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=561</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=562</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=563</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=564</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=565</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=566</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=567</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=568</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=569</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=570</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=571</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=572</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=573</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=574</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=575</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=576</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=577</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=578</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=579</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=580</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=581</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=582</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=583</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=584</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=585</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=586</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=587</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=588</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=589</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=590</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=591</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=592</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=593</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=594</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=595</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=596</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=597</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=598</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=599</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=600</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=601</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=602</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=603</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=604</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=605</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=606</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=607</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=608</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=609</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=610</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=611</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=612</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=613</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=614</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=615</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=616</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=617</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=618</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=619</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=620</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=621</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=622</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=623</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=624</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=625</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=626</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=631</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=632</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=633</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=634</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=635</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=636</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=637</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=638</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=639</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=640</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=641</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=642</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=643</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=644</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=645</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=646</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=647</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=648</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=649</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=650</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=651</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=652</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=653</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=654</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=655</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=656</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=657</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=658</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=659</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=660</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=661</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=662</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=663</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=664</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=665</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=666</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=667</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=668</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=669</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=670</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=671</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=672</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=673</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=674</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=675</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=676</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=677</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=678</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=679</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=680</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=681</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=682</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=683</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=684</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=685</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=686</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=687</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=688</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=689</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=690</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=691</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=692</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=693</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=694</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=695</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=696</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=697</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=698</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=699</t>
+  </si>
+  <si>
+    <t>https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=700</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1401,6 +3646,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1423,10 +3675,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1761,6 +4014,4085 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1EF60B-5488-7341-B925-A1F99F3F008B}">
+  <dimension ref="A1:B505"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>483</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>484</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>485</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>486</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488">
+        <v>487</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>488</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490">
+        <v>489</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491">
+        <v>490</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492">
+        <v>491</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493">
+        <v>492</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494">
+        <v>493</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495">
+        <v>494</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A496">
+        <v>495</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A497">
+        <v>496</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A498">
+        <v>497</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A499">
+        <v>498</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A500">
+        <v>499</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A502">
+        <v>501</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A503">
+        <v>502</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A504">
+        <v>503</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A505">
+        <v>504</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{F8F6BCD2-FA03-EA44-A0A8-DD1D25831F78}"/>
+    <hyperlink ref="B11:B27" r:id="rId2" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=167" xr:uid="{E89481D5-CC64-8049-A7A7-A76AF3BC8A8E}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{DA51A916-0DC2-A640-A870-53889902B88B}"/>
+    <hyperlink ref="B27" r:id="rId4" xr:uid="{49E575DD-93C1-0844-ADB7-AB793082E5F0}"/>
+    <hyperlink ref="B29:B33" r:id="rId5" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=189" xr:uid="{FB9BDFAF-A56F-7346-9F19-1D1547176A6C}"/>
+    <hyperlink ref="B34" r:id="rId6" xr:uid="{589F655C-FCED-2B45-8ED6-AE0C3211D7C3}"/>
+    <hyperlink ref="B35:B61" r:id="rId7" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=199" xr:uid="{9830C2B4-1719-F14E-A36A-127D7D9740DC}"/>
+    <hyperlink ref="B62" r:id="rId8" xr:uid="{29801C04-30CA-884B-9DC3-B550B5C3AB0F}"/>
+    <hyperlink ref="B63" r:id="rId9" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=231" xr:uid="{AFF1C257-FA47-704C-A4DF-E21C820198F0}"/>
+    <hyperlink ref="B64" r:id="rId10" xr:uid="{1C6C28C0-A7EC-214C-B1D5-F151BADD65C1}"/>
+    <hyperlink ref="B65" r:id="rId11" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=237" xr:uid="{A6E97966-07CA-814C-BA91-AA86B0048798}"/>
+    <hyperlink ref="B66" r:id="rId12" xr:uid="{48FD79EC-9544-B643-A264-344531DFC859}"/>
+    <hyperlink ref="B67:B75" r:id="rId13" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=243" xr:uid="{B26E4B93-AD99-3342-8DCD-C3ED9FEC849D}"/>
+    <hyperlink ref="B76" r:id="rId14" xr:uid="{279424BC-5AC2-3746-9F40-13E2DB443532}"/>
+    <hyperlink ref="B77:B83" r:id="rId15" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=257" xr:uid="{8FE276B5-7FE6-5141-A651-D0318B38A696}"/>
+    <hyperlink ref="B84" r:id="rId16" xr:uid="{0EFC3351-5FBA-184E-A290-03B28AA97184}"/>
+    <hyperlink ref="B85:B94" r:id="rId17" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=269" xr:uid="{4A54FEF4-D1F6-B94A-8EAD-1CD07E5BF31D}"/>
+    <hyperlink ref="B96" r:id="rId18" xr:uid="{FEDA5DA7-6973-3641-9D8A-CCBBB5C3079B}"/>
+    <hyperlink ref="B97:B147" r:id="rId19" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=283" xr:uid="{AC1A192F-1CB2-5A47-964D-1E260FCC99E3}"/>
+    <hyperlink ref="B148" r:id="rId20" xr:uid="{9312F86F-8A9D-9948-81CE-B440245FBEC2}"/>
+    <hyperlink ref="B149:B435" r:id="rId21" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=339" xr:uid="{C781CCFD-3863-5F43-8FA9-E63DF543465B}"/>
+    <hyperlink ref="B436" r:id="rId22" xr:uid="{8AC7F3BB-7D4B-184E-BA6E-D369898CEDE1}"/>
+    <hyperlink ref="B437:B505" r:id="rId23" display="https://hdl.handle.net/2027/mdp.39015016921887?urlappend=%3Bseq=631" xr:uid="{278A69F8-2D3A-6D41-9ACB-9FD5AF0D623F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB1A6D3-2B08-7143-9BC0-FDAD321D8564}">
   <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4213,7 +10545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F66F897-60FD-7748-B6D6-4E69725118BE}">
   <dimension ref="A1:B153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5459,4 +11791,2030 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B46086-7E5C-4845-B1F3-6D1D4B842AD3}">
+  <dimension ref="A1:B108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>50</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>51</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>52</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>53</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>54</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>55</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>56</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>57</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>58</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>59</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>61</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>62</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>63</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>64</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>65</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>67</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>68</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>69</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>72</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>74</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>76</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>78</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>81</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>82</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>83</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>84</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>85</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>86</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>87</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>88</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>89</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>90</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>91</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>92</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>93</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>94</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>95</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>96</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>97</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>98</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>99</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>100</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>101</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>102</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>103</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>104</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>105</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>106</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>107</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>108</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>109</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B48" r:id="rId1" xr:uid="{85B71DCF-1D15-D743-8002-07143DB89DC2}"/>
+    <hyperlink ref="B49:B51" r:id="rId2" display="https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=67" xr:uid="{1B756589-4A92-F54F-90C7-DAC6E19BE422}"/>
+    <hyperlink ref="B52" r:id="rId3" xr:uid="{BEC6CACF-80B6-C043-A54E-28BA1700B94E}"/>
+    <hyperlink ref="B53:B108" r:id="rId4" display="https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=75" xr:uid="{9A17EC90-4240-A148-8441-4013F22C0BDC}"/>
+    <hyperlink ref="B86" r:id="rId5" xr:uid="{C46A0025-584E-8C4E-87BE-37FA19FFC45E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1CC0CB-A80D-8B40-8186-BC1D24E8716A}">
+  <dimension ref="A1:B111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>37</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>39</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>42</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>43</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>45</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>46</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>47</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>49</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>50</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>51</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>52</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>53</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>54</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>55</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>56</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>57</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>58</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>59</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>60</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>61</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>62</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>63</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>64</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>65</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>66</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>67</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>68</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>69</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>70</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>71</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>72</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>73</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>74</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>75</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>76</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>77</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>78</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>79</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>80</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>81</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>82</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>83</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>84</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>85</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>86</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>87</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>88</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>89</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>90</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>91</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>92</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>93</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>94</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>95</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>96</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>97</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>98</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>99</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>100</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>101</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>102</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>103</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>104</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>105</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>106</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>107</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>108</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>109</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>110</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>111</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>112</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>113</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>114</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>115</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>116</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>117</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>118</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>119</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>120</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>121</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>122</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>123</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>124</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>125</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{8BFE5204-682B-4741-A607-A42C361BAF76}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{28570FA5-AE4A-3F42-BD28-FE63AE974DE9}"/>
+    <hyperlink ref="B4:B111" r:id="rId3" display="https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=155" xr:uid="{3ACBED79-273C-D54B-9AD9-8CA576889C81}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493A955A-4E91-C142-88B2-1D09A910797F}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>128</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>129</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>130</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>131</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>132</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>133</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>134</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>135</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>136</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>137</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>138</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>139</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>140</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>141</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>142</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>143</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>144</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>145</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>146</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>147</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>148</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>149</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>150</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>151</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>152</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>153</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{A7856E0B-EB2C-9144-9221-A63498851B6F}"/>
+    <hyperlink ref="B3:B27" r:id="rId2" display="https://hdl.handle.net/2027/mdp.39015066184931?urlappend=%3Bseq=266" xr:uid="{ECDE34CD-A9C8-0E46-A42F-9FC22DE8A261}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>